--- a/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
@@ -420,7 +420,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.2125984251968504</v>
+        <v>0.2248062015503876</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -429,16 +429,16 @@
         <v>0.2605633802816901</v>
       </c>
       <c r="D2">
-        <v>0.7954545454545454</v>
+        <v>0.7835820895522388</v>
       </c>
       <c r="E2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F2">
         <v>5</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
